--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -10564,7 +10564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="26" customWidth="1" style="6" min="1" max="2"/>
@@ -10592,6 +10592,16 @@
           <t>נושא</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>תנועת עבר (a/i/u)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>תנועת הווה (a/i/u)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="6">
       <c r="A2" s="4" t="inlineStr">
@@ -10614,6 +10624,16 @@
           <t>תקשורת וכתיבה</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="6">
       <c r="A3" s="4" t="inlineStr">
@@ -10636,6 +10656,16 @@
           <t>קוגניטיבי</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="6">
       <c r="A4" s="4" t="inlineStr">
@@ -10658,6 +10688,16 @@
           <t>חושים</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="6">
       <c r="A5" s="4" t="inlineStr">
@@ -10680,6 +10720,16 @@
           <t>אכילה ושתייה</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10702,6 +10752,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="6">
       <c r="A7" s="4" t="inlineStr">
@@ -10724,6 +10784,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="4" t="inlineStr">
@@ -10746,6 +10816,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="6">
       <c r="A9" s="4" t="inlineStr">
@@ -10768,6 +10848,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="6">
       <c r="A10" s="4" t="inlineStr">
@@ -10790,6 +10880,16 @@
           <t>פעולות גוף</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="6">
       <c r="A11" s="4" t="inlineStr">
@@ -10812,6 +10912,16 @@
           <t>חושים</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="4" t="inlineStr">
@@ -10834,6 +10944,16 @@
           <t>עבודה</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="6">
       <c r="A13" s="4" t="inlineStr">
@@ -10856,6 +10976,16 @@
           <t>פנאי</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="6">
       <c r="A14" s="4" t="inlineStr">
@@ -10878,6 +11008,16 @@
           <t>לימודים</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="6">
       <c r="A15" s="4" t="inlineStr">
@@ -10900,6 +11040,16 @@
           <t>פעולות יומיומיות</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="6">
       <c r="A16" s="4" t="inlineStr">
@@ -10922,6 +11072,16 @@
           <t>פעולות יומיומיות</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="6">
       <c r="A17" s="4" t="inlineStr">
@@ -10944,6 +11104,16 @@
           <t>תקשורת</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="6">
       <c r="A18" s="4" t="inlineStr">
@@ -10966,6 +11136,16 @@
           <t>קוגניטיבי</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="6">
       <c r="A19" s="4" t="inlineStr">
@@ -10988,6 +11168,16 @@
           <t>קוגניטיבי</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="6">
       <c r="A20" s="4" t="inlineStr">
@@ -11010,6 +11200,16 @@
           <t>פעולות פיזיות</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="6">
       <c r="A21" s="4" t="inlineStr">
@@ -11032,6 +11232,16 @@
           <t>בית</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="6">
       <c r="A22" s="4" t="inlineStr">
@@ -11054,6 +11264,16 @@
           <t>לבוש</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="6">
       <c r="A23" s="4" t="inlineStr">
@@ -11076,6 +11296,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="6">
       <c r="A24" s="4" t="inlineStr">
@@ -11098,6 +11328,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="6">
       <c r="A25" s="4" t="inlineStr">
@@ -11120,6 +11360,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="6">
       <c r="A26" s="4" t="inlineStr">
@@ -11142,6 +11392,16 @@
           <t>עבודה</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="6">
       <c r="A27" s="4" t="inlineStr">
@@ -11164,6 +11424,16 @@
           <t>אמנות</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="6">
       <c r="A28" s="4" t="inlineStr">
@@ -11186,6 +11456,16 @@
           <t>בית</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="6">
       <c r="A29" s="4" t="inlineStr">
@@ -11208,6 +11488,16 @@
           <t>טבע</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="6">
       <c r="A30" s="4" t="inlineStr">
@@ -11230,6 +11520,16 @@
           <t>פעולות פיזיות</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="6">
       <c r="A31" s="4" t="inlineStr">
@@ -11252,6 +11552,16 @@
           <t>פעולות פיזיות</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="6">
       <c r="A32" s="4" t="inlineStr">
@@ -11274,6 +11584,16 @@
           <t>פעולות פיזיות</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="6">
       <c r="A33" s="4" t="inlineStr">
@@ -11296,6 +11616,16 @@
           <t>פעולות פיזיות</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="6">
       <c r="A34" s="4" t="inlineStr">
@@ -11318,6 +11648,16 @@
           <t>פעולות פיזיות</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="6">
       <c r="A35" s="4" t="inlineStr">
@@ -11340,6 +11680,16 @@
           <t>ממשל ומשפט</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="6">
       <c r="A36" s="4" t="inlineStr">
@@ -11362,6 +11712,16 @@
           <t>הישגים</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="6">
       <c r="A37" s="4" t="inlineStr">
@@ -11384,6 +11744,16 @@
           <t>הישגים</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="6">
       <c r="A38" s="4" t="inlineStr">
@@ -11406,6 +11776,16 @@
           <t>פנאי</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="6">
       <c r="A39" s="4" t="inlineStr">
@@ -11428,6 +11808,16 @@
           <t>רגשות</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="6">
       <c r="A40" s="4" t="inlineStr">
@@ -11450,6 +11840,16 @@
           <t>תנועה</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="6">
       <c r="A41" s="4" t="inlineStr">
@@ -11470,6 +11870,16 @@
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>פנאי / ספורט</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>a</t>
         </is>
       </c>
     </row>

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -20770,7 +20770,7 @@
     <row r="505">
       <c r="A505" s="10" t="inlineStr">
         <is>
-          <t>شَرَبَ</t>
+          <t>شَرِبَ</t>
         </is>
       </c>
       <c r="B505" s="11" t="n"/>
@@ -20794,7 +20794,7 @@
     <row r="507">
       <c r="A507" s="10" t="inlineStr">
         <is>
-          <t>اِرْجَعْ</t>
+          <t>اِرْجِعْ</t>
         </is>
       </c>
       <c r="B507" s="11" t="n"/>
@@ -20818,7 +20818,7 @@
     <row r="509">
       <c r="A509" s="10" t="inlineStr">
         <is>
-          <t>تَدْخَلُونَ</t>
+          <t>تَدْخُلُونَ</t>
         </is>
       </c>
       <c r="B509" s="11" t="n"/>
@@ -20830,7 +20830,7 @@
     <row r="510">
       <c r="A510" s="10" t="inlineStr">
         <is>
-          <t>اِجْلَسُوا</t>
+          <t>اِجْلِسُوا</t>
         </is>
       </c>
       <c r="B510" s="11" t="n"/>
@@ -20902,7 +20902,7 @@
     <row r="516">
       <c r="A516" s="10" t="inlineStr">
         <is>
-          <t>اِغْلَقْنَ</t>
+          <t>اِغْلِقْنَ</t>
         </is>
       </c>
       <c r="B516" s="11" t="n"/>
@@ -20926,7 +20926,7 @@
     <row r="518">
       <c r="A518" s="10" t="inlineStr">
         <is>
-          <t>يَعْرَفُ</t>
+          <t>يَعْرِفُ</t>
         </is>
       </c>
       <c r="B518" s="11" t="n"/>
@@ -20962,7 +20962,7 @@
     <row r="521">
       <c r="A521" s="10" t="inlineStr">
         <is>
-          <t>تَغْسَلَانِ</t>
+          <t>تَغْسِلَانِ</t>
         </is>
       </c>
       <c r="B521" s="11" t="n"/>
@@ -20986,7 +20986,7 @@
     <row r="523">
       <c r="A523" s="10" t="inlineStr">
         <is>
-          <t>رَكَبْتُنَّ</t>
+          <t>رَكِبْتُنَّ</t>
         </is>
       </c>
       <c r="B523" s="11" t="n"/>
@@ -20998,7 +20998,7 @@
     <row r="524">
       <c r="A524" s="10" t="inlineStr">
         <is>
-          <t>يَنْزَلَانِ</t>
+          <t>يَنْزِلَانِ</t>
         </is>
       </c>
       <c r="B524" s="11" t="n"/>
@@ -21034,7 +21034,7 @@
     <row r="527">
       <c r="A527" s="10" t="inlineStr">
         <is>
-          <t>يَرْسَمْنَ</t>
+          <t>يَرْسُمْنَ</t>
         </is>
       </c>
       <c r="B527" s="11" t="n"/>
@@ -21046,7 +21046,7 @@
     <row r="528">
       <c r="A528" s="10" t="inlineStr">
         <is>
-          <t>اِطْبَخِي</t>
+          <t>اُطْبُخِي</t>
         </is>
       </c>
       <c r="B528" s="11" t="n"/>
@@ -21070,7 +21070,7 @@
     <row r="530">
       <c r="A530" s="10" t="inlineStr">
         <is>
-          <t>تَحْمَلِينَ</t>
+          <t>تَحْمِلِينَ</t>
         </is>
       </c>
       <c r="B530" s="11" t="n"/>
@@ -21118,7 +21118,7 @@
     <row r="534">
       <c r="A534" s="10" t="inlineStr">
         <is>
-          <t>اِضْرَبَا</t>
+          <t>اِضْرِبَا</t>
         </is>
       </c>
       <c r="B534" s="11" t="n"/>
@@ -21190,7 +21190,7 @@
     <row r="540">
       <c r="A540" s="10" t="inlineStr">
         <is>
-          <t>اِقْفَزُوا</t>
+          <t>اِقْفِزُوا</t>
         </is>
       </c>
       <c r="B540" s="11" t="n"/>
@@ -21214,7 +21214,7 @@
     <row r="542">
       <c r="A542" s="10" t="inlineStr">
         <is>
-          <t>تَكْتَبُ</t>
+          <t>تَكْتُبُ</t>
         </is>
       </c>
       <c r="B542" s="11" t="n"/>
@@ -21238,7 +21238,7 @@
     <row r="544">
       <c r="A544" s="10" t="inlineStr">
         <is>
-          <t>سَمَعَ</t>
+          <t>سَمِعَ</t>
         </is>
       </c>
       <c r="B544" s="11" t="n"/>
@@ -21286,7 +21286,7 @@
     <row r="548">
       <c r="A548" s="10" t="inlineStr">
         <is>
-          <t>تَخْرَجُونَ</t>
+          <t>تَخْرُجُونَ</t>
         </is>
       </c>
       <c r="B548" s="11" t="n"/>
@@ -21298,7 +21298,7 @@
     <row r="549">
       <c r="A549" s="10" t="inlineStr">
         <is>
-          <t>اِدْخَلَا</t>
+          <t>اُدْخُلَا</t>
         </is>
       </c>
       <c r="B549" s="11" t="n"/>
@@ -21322,7 +21322,7 @@
     <row r="551">
       <c r="A551" s="10" t="inlineStr">
         <is>
-          <t>تَنْظَرَانِ</t>
+          <t>تَنْظُرَانِ</t>
         </is>
       </c>
       <c r="B551" s="11" t="n"/>
@@ -37484,7 +37484,7 @@
     <row r="505">
       <c r="A505" s="10" t="inlineStr">
         <is>
-          <t>شَرَبَ</t>
+          <t>شَرِبَ</t>
         </is>
       </c>
       <c r="B505" s="10" t="inlineStr">
@@ -37548,7 +37548,7 @@
     <row r="507">
       <c r="A507" s="10" t="inlineStr">
         <is>
-          <t>اِرْجَعْ</t>
+          <t>اِرْجِعْ</t>
         </is>
       </c>
       <c r="B507" s="10" t="inlineStr">
@@ -37612,7 +37612,7 @@
     <row r="509">
       <c r="A509" s="10" t="inlineStr">
         <is>
-          <t>تَدْخَلُونَ</t>
+          <t>تَدْخُلُونَ</t>
         </is>
       </c>
       <c r="B509" s="10" t="inlineStr">
@@ -37644,7 +37644,7 @@
     <row r="510">
       <c r="A510" s="10" t="inlineStr">
         <is>
-          <t>اِجْلَسُوا</t>
+          <t>اِجْلِسُوا</t>
         </is>
       </c>
       <c r="B510" s="10" t="inlineStr">
@@ -37836,7 +37836,7 @@
     <row r="516">
       <c r="A516" s="10" t="inlineStr">
         <is>
-          <t>اِغْلَقْنَ</t>
+          <t>اِغْلِقْنَ</t>
         </is>
       </c>
       <c r="B516" s="10" t="inlineStr">
@@ -37900,7 +37900,7 @@
     <row r="518">
       <c r="A518" s="10" t="inlineStr">
         <is>
-          <t>يَعْرَفُ</t>
+          <t>يَعْرِفُ</t>
         </is>
       </c>
       <c r="B518" s="10" t="inlineStr">
@@ -37996,7 +37996,7 @@
     <row r="521">
       <c r="A521" s="10" t="inlineStr">
         <is>
-          <t>تَغْسَلَانِ</t>
+          <t>تَغْسِلَانِ</t>
         </is>
       </c>
       <c r="B521" s="10" t="inlineStr">
@@ -38060,7 +38060,7 @@
     <row r="523">
       <c r="A523" s="10" t="inlineStr">
         <is>
-          <t>رَكَبْتُنَّ</t>
+          <t>رَكِبْتُنَّ</t>
         </is>
       </c>
       <c r="B523" s="10" t="inlineStr">
@@ -38092,7 +38092,7 @@
     <row r="524">
       <c r="A524" s="10" t="inlineStr">
         <is>
-          <t>يَنْزَلَانِ</t>
+          <t>يَنْزِلَانِ</t>
         </is>
       </c>
       <c r="B524" s="10" t="inlineStr">
@@ -38188,7 +38188,7 @@
     <row r="527">
       <c r="A527" s="10" t="inlineStr">
         <is>
-          <t>يَرْسَمْنَ</t>
+          <t>يَرْسُمْنَ</t>
         </is>
       </c>
       <c r="B527" s="10" t="inlineStr">
@@ -38220,7 +38220,7 @@
     <row r="528">
       <c r="A528" s="10" t="inlineStr">
         <is>
-          <t>اِطْبَخِي</t>
+          <t>اُطْبُخِي</t>
         </is>
       </c>
       <c r="B528" s="10" t="inlineStr">
@@ -38284,7 +38284,7 @@
     <row r="530">
       <c r="A530" s="10" t="inlineStr">
         <is>
-          <t>تَحْمَلِينَ</t>
+          <t>تَحْمِلِينَ</t>
         </is>
       </c>
       <c r="B530" s="10" t="inlineStr">
@@ -38412,7 +38412,7 @@
     <row r="534">
       <c r="A534" s="10" t="inlineStr">
         <is>
-          <t>اِضْرَبَا</t>
+          <t>اِضْرِبَا</t>
         </is>
       </c>
       <c r="B534" s="10" t="inlineStr">
@@ -38604,7 +38604,7 @@
     <row r="540">
       <c r="A540" s="10" t="inlineStr">
         <is>
-          <t>اِقْفَزُوا</t>
+          <t>اِقْفِزُوا</t>
         </is>
       </c>
       <c r="B540" s="10" t="inlineStr">
@@ -38668,7 +38668,7 @@
     <row r="542">
       <c r="A542" s="10" t="inlineStr">
         <is>
-          <t>تَكْتَبُ</t>
+          <t>تَكْتُبُ</t>
         </is>
       </c>
       <c r="B542" s="10" t="inlineStr">
@@ -38732,7 +38732,7 @@
     <row r="544">
       <c r="A544" s="10" t="inlineStr">
         <is>
-          <t>سَمَعَ</t>
+          <t>سَمِعَ</t>
         </is>
       </c>
       <c r="B544" s="10" t="inlineStr">
@@ -38860,7 +38860,7 @@
     <row r="548">
       <c r="A548" s="10" t="inlineStr">
         <is>
-          <t>تَخْرَجُونَ</t>
+          <t>تَخْرُجُونَ</t>
         </is>
       </c>
       <c r="B548" s="10" t="inlineStr">
@@ -38892,7 +38892,7 @@
     <row r="549">
       <c r="A549" s="10" t="inlineStr">
         <is>
-          <t>اِدْخَلَا</t>
+          <t>اُدْخُلَا</t>
         </is>
       </c>
       <c r="B549" s="10" t="inlineStr">
@@ -38956,7 +38956,7 @@
     <row r="551">
       <c r="A551" s="10" t="inlineStr">
         <is>
-          <t>تَنْظَرَانِ</t>
+          <t>تَنْظُرَانِ</t>
         </is>
       </c>
       <c r="B551" s="10" t="inlineStr">

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:F403"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="9" customWidth="1" style="6" min="1" max="1"/>
@@ -542,6 +542,11 @@
           <t>תעתיק</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>מילה מנוקדת</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="6">
       <c r="A2" s="2" t="n">
@@ -567,6 +572,11 @@
           <t>מרחבא</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>مَرْحَبًا</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="6">
       <c r="A3" s="2" t="n">
@@ -592,6 +602,11 @@
           <t>אהלא</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>أَهْلًا</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="6">
       <c r="A4" s="2" t="n">
@@ -617,6 +632,11 @@
           <t>אלסלאמ עליכמ</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>اَلسَّلَامُ عَلَيْكُمْ</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="6">
       <c r="A5" s="2" t="n">
@@ -642,6 +662,11 @@
           <t>ודאעא</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>وَدَاعًا</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="6">
       <c r="A6" s="2" t="n">
@@ -667,6 +692,11 @@
           <t>מע אלסלאמה</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>مَعَ السَّلَامَة</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="6">
       <c r="A7" s="2" t="n">
@@ -692,6 +722,11 @@
           <t>נעמ</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>نَعَمْ</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="2" t="n">
@@ -717,6 +752,11 @@
           <t>לא</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>لَا</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="6">
       <c r="A9" s="2" t="n">
@@ -742,6 +782,11 @@
           <t>מנ פדלכ</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>مِنْ فَضْلِكَ</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="6">
       <c r="A10" s="2" t="n">
@@ -767,6 +812,11 @@
           <t>שכרא</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>شُكْرًا</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="6">
       <c r="A11" s="2" t="n">
@@ -792,6 +842,11 @@
           <t>עפוא</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>عَفْوًا</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="2" t="n">
@@ -817,6 +872,11 @@
           <t>אספ</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>آسِف</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="6">
       <c r="A13" s="2" t="n">
@@ -842,6 +902,11 @@
           <t>צבאח אלח'יר</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>صَبَاحُ الْخَير</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="6">
       <c r="A14" s="2" t="n">
@@ -867,6 +932,11 @@
           <t>מסאא אלח'יר</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>مَسَاءُ الْخَير</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="6">
       <c r="A15" s="2" t="n">
@@ -892,6 +962,11 @@
           <t>תצבח עלא ח'יר</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>تُصْبِحُ عَلَى خَيْر</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="6">
       <c r="A16" s="2" t="n">
@@ -917,6 +992,11 @@
           <t>כיפ חאלכ</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>كَيْفَ حَالُكَ</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="6">
       <c r="A17" s="2" t="n">
@@ -942,6 +1022,11 @@
           <t>בח'יר</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>بِخَيْر</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="6">
       <c r="A18" s="2" t="n">
@@ -967,6 +1052,11 @@
           <t>מא אסמכ</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>مَا اسْمُكَ</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="6">
       <c r="A19" s="2" t="n">
@@ -992,6 +1082,11 @@
           <t>אסמי</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>اِسْمِي</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="6">
       <c r="A20" s="2" t="n">
@@ -1017,6 +1112,11 @@
           <t>מנ</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>مَنْ</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="6">
       <c r="A21" s="2" t="n">
@@ -1042,6 +1142,11 @@
           <t>מאד'א</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>مَاذَا</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="6">
       <c r="A22" s="2" t="n">
@@ -1067,6 +1172,11 @@
           <t>אינ</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>أَيْنَ</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="6">
       <c r="A23" s="2" t="n">
@@ -1092,6 +1202,11 @@
           <t>מתא</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>مَتَى</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="6">
       <c r="A24" s="2" t="n">
@@ -1117,6 +1232,11 @@
           <t>למאד'א</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>لِمَاذَا</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="6">
       <c r="A25" s="2" t="n">
@@ -1142,6 +1262,11 @@
           <t>כיפ</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>كَيْفَ</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="6">
       <c r="A26" s="2" t="n">
@@ -1167,6 +1292,11 @@
           <t>כמ</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>كَمْ</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="6">
       <c r="A27" s="2" t="n">
@@ -1192,6 +1322,11 @@
           <t>אי</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>أَيّ</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="6">
       <c r="A28" s="2" t="n">
@@ -1217,6 +1352,11 @@
           <t>הל</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>هَلْ</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="6">
       <c r="A29" s="2" t="n">
@@ -1242,6 +1382,11 @@
           <t>ו</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>وَ</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="6">
       <c r="A30" s="2" t="n">
@@ -1267,6 +1412,11 @@
           <t>או</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>أَوْ</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="6">
       <c r="A31" s="2" t="n">
@@ -1292,6 +1442,11 @@
           <t>לכנ</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>لَكِنْ</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="6">
       <c r="A32" s="2" t="n">
@@ -1317,6 +1472,11 @@
           <t>כמאנ</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>كَمَان</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="6">
       <c r="A33" s="2" t="n">
@@ -1342,6 +1502,11 @@
           <t>אלאנ</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>اَلْآنَ</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="6">
       <c r="A34" s="2" t="n">
@@ -1367,6 +1532,11 @@
           <t>הנא</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>هُنَا</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="6">
       <c r="A35" s="2" t="n">
@@ -1392,6 +1562,11 @@
           <t>הנאכ</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>هُنَاكَ</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="6">
       <c r="A36" s="2" t="n">
@@ -1417,6 +1592,11 @@
           <t>באלטבע/טבעאן</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>بِالطَّبْع / طَبْعًا</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="6">
       <c r="A37" s="2" t="n">
@@ -1442,6 +1622,11 @@
           <t>ג'יד</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>جَيِّد</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="6">
       <c r="A38" s="2" t="n">
@@ -1467,6 +1652,11 @@
           <t>סיא</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>سَيِّئ</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="6">
       <c r="A39" s="2" t="n">
@@ -1492,6 +1682,11 @@
           <t>ג'דיד</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>جَدِيد</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="6">
       <c r="A40" s="2" t="n">
@@ -1517,6 +1712,11 @@
           <t>קדימ</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>قَدِيم</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="6">
       <c r="A41" s="2" t="n">
@@ -1540,6 +1740,11 @@
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>ערבי</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>عَرَبِيّ</t>
         </is>
       </c>
     </row>

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F403"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="9" customWidth="1" style="6" min="1" max="1"/>
@@ -542,11 +542,6 @@
           <t>תעתיק</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>מילה מנוקדת</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="6">
       <c r="A2" s="2" t="n">
@@ -572,11 +567,6 @@
           <t>מרחבא</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>مَرْحَبًا</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="6">
       <c r="A3" s="2" t="n">
@@ -602,11 +592,6 @@
           <t>אהלא</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>أَهْلًا</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="6">
       <c r="A4" s="2" t="n">
@@ -632,11 +617,6 @@
           <t>אלסלאמ עליכמ</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>اَلسَّلَامُ عَلَيْكُمْ</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="6">
       <c r="A5" s="2" t="n">
@@ -662,11 +642,6 @@
           <t>ודאעא</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>وَدَاعًا</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="6">
       <c r="A6" s="2" t="n">
@@ -692,11 +667,6 @@
           <t>מע אלסלאמה</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>مَعَ السَّلَامَة</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="6">
       <c r="A7" s="2" t="n">
@@ -722,11 +692,6 @@
           <t>נעמ</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>نَعَمْ</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="6">
       <c r="A8" s="2" t="n">
@@ -752,11 +717,6 @@
           <t>לא</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>لَا</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="6">
       <c r="A9" s="2" t="n">
@@ -782,11 +742,6 @@
           <t>מנ פדלכ</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>مِنْ فَضْلِكَ</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="6">
       <c r="A10" s="2" t="n">
@@ -812,11 +767,6 @@
           <t>שכרא</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>شُكْرًا</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="6">
       <c r="A11" s="2" t="n">
@@ -842,11 +792,6 @@
           <t>עפוא</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>عَفْوًا</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="6">
       <c r="A12" s="2" t="n">
@@ -872,11 +817,6 @@
           <t>אספ</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>آسِف</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="6">
       <c r="A13" s="2" t="n">
@@ -902,11 +842,6 @@
           <t>צבאח אלח'יר</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>صَبَاحُ الْخَير</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="6">
       <c r="A14" s="2" t="n">
@@ -932,11 +867,6 @@
           <t>מסאא אלח'יר</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>مَسَاءُ الْخَير</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="6">
       <c r="A15" s="2" t="n">
@@ -962,11 +892,6 @@
           <t>תצבח עלא ח'יר</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>تُصْبِحُ عَلَى خَيْر</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="6">
       <c r="A16" s="2" t="n">
@@ -992,11 +917,6 @@
           <t>כיפ חאלכ</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>كَيْفَ حَالُكَ</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="6">
       <c r="A17" s="2" t="n">
@@ -1022,11 +942,6 @@
           <t>בח'יר</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>بِخَيْر</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="6">
       <c r="A18" s="2" t="n">
@@ -1052,11 +967,6 @@
           <t>מא אסמכ</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>مَا اسْمُكَ</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="6">
       <c r="A19" s="2" t="n">
@@ -1082,11 +992,6 @@
           <t>אסמי</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>اِسْمِي</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="6">
       <c r="A20" s="2" t="n">
@@ -1112,11 +1017,6 @@
           <t>מנ</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>مَنْ</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="6">
       <c r="A21" s="2" t="n">
@@ -1142,11 +1042,6 @@
           <t>מאד'א</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>مَاذَا</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="6">
       <c r="A22" s="2" t="n">
@@ -1172,11 +1067,6 @@
           <t>אינ</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>أَيْنَ</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="6">
       <c r="A23" s="2" t="n">
@@ -1202,11 +1092,6 @@
           <t>מתא</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>مَتَى</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="6">
       <c r="A24" s="2" t="n">
@@ -1232,11 +1117,6 @@
           <t>למאד'א</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>لِمَاذَا</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="6">
       <c r="A25" s="2" t="n">
@@ -1262,11 +1142,6 @@
           <t>כיפ</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>كَيْفَ</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="6">
       <c r="A26" s="2" t="n">
@@ -1292,11 +1167,6 @@
           <t>כמ</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>كَمْ</t>
-        </is>
-      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="6">
       <c r="A27" s="2" t="n">
@@ -1322,11 +1192,6 @@
           <t>אי</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>أَيّ</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="6">
       <c r="A28" s="2" t="n">
@@ -1352,11 +1217,6 @@
           <t>הל</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>هَلْ</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="6">
       <c r="A29" s="2" t="n">
@@ -1382,11 +1242,6 @@
           <t>ו</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>وَ</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="6">
       <c r="A30" s="2" t="n">
@@ -1412,11 +1267,6 @@
           <t>או</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>أَوْ</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="6">
       <c r="A31" s="2" t="n">
@@ -1442,11 +1292,6 @@
           <t>לכנ</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>لَكِنْ</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="6">
       <c r="A32" s="2" t="n">
@@ -1472,11 +1317,6 @@
           <t>כמאנ</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>كَمَان</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="6">
       <c r="A33" s="2" t="n">
@@ -1502,11 +1342,6 @@
           <t>אלאנ</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>اَلْآنَ</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="6">
       <c r="A34" s="2" t="n">
@@ -1532,11 +1367,6 @@
           <t>הנא</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>هُنَا</t>
-        </is>
-      </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="6">
       <c r="A35" s="2" t="n">
@@ -1562,11 +1392,6 @@
           <t>הנאכ</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>هُنَاكَ</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="6">
       <c r="A36" s="2" t="n">
@@ -1592,11 +1417,6 @@
           <t>באלטבע/טבעאן</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>بِالطَّبْع / طَبْعًا</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="6">
       <c r="A37" s="2" t="n">
@@ -1622,11 +1442,6 @@
           <t>ג'יד</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>جَيِّد</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="6">
       <c r="A38" s="2" t="n">
@@ -1652,11 +1467,6 @@
           <t>סיא</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>سَيِّئ</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="6">
       <c r="A39" s="2" t="n">
@@ -1682,11 +1492,6 @@
           <t>ג'דיד</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>جَدِيد</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="6">
       <c r="A40" s="2" t="n">
@@ -1712,11 +1517,6 @@
           <t>קדימ</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>قَدِيم</t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="6">
       <c r="A41" s="2" t="n">
@@ -1740,11 +1540,6 @@
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>ערבי</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>عَرَبِيّ</t>
         </is>
       </c>
     </row>

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -125,6 +125,9 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,8 +499,9 @@
     <col width="9" customWidth="1" style="9" min="1" max="1"/>
     <col width="30" customWidth="1" style="9" min="2" max="2"/>
     <col width="22" customWidth="1" style="9" min="3" max="3"/>
-    <col width="26" customWidth="1" style="9" min="4" max="4"/>
-    <col width="22" customWidth="1" style="9" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="9" min="4" max="4"/>
+    <col width="26" customWidth="1" style="9" min="5" max="5"/>
+    <col width="16.83203125" customWidth="1" style="9" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" s="9">
@@ -1125,7 +1129,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>إِلىَ</t>
+          <t>إِلَى</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1281,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>أِمْس</t>
+          <t>أَمْسِ</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>أَنْتنّ</t>
+          <t>أَنْتُنَّ</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>بَين</t>
+          <t>بَينَ</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2481,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>تمرِين</t>
+          <t>تَمْرِين</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8202,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>أالله</t>
+          <t>الله</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8208,12 +8212,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>אאללה</t>
+          <t>אללה</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>أَالله</t>
+          <t>الله</t>
         </is>
       </c>
     </row>
@@ -10671,7 +10675,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>سَمَِع</t>
+          <t>سَمِعَ</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -11129,7 +11133,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>شّمََالي</t>
+          <t>شَّمَالي</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11376,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>طَريق</t>
+          <t>طَرِيق</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -11534,7 +11538,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>عائِلَة</t>
+          <t>عَائِلَة</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12420,7 +12424,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>فِيلم</t>
+          <t>فِيلْم</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -12873,7 +12877,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>كُرْسِيٍّ</t>
+          <t>كُرْسِي</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -12916,7 +12920,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>كَلام</t>
+          <t>كَلَام</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -13040,7 +13044,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>مَتىَ</t>
+          <t>مَتَى</t>
         </is>
       </c>
     </row>
@@ -13240,7 +13244,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>مَسَاءُ الْخَير</t>
+          <t>مَسَاء الْخَير</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -13369,7 +13373,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>مَسِيحِيَّ</t>
+          <t>مَسِيحِيِّ</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -13574,7 +13578,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>نَبيِّ</t>
+          <t>نَبِّي</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13731,7 +13735,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>وَراءَ</t>
+          <t>وَرَاء</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14110,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>إجتمعب مع</t>
+          <t>إجتمع مع</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -14116,12 +14120,12 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>אג׳תמעב מע</t>
+          <t>אג׳תמע מע</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>إَجْتَمَعَبِ مَع</t>
+          <t>إَجْتَمَعَ مَع</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14396,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>إِسْترَِاحَة</t>
+          <t>إِسْتِرَاحَة</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14472,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>إِسْتَمَعََ إلى</t>
+          <t>إِسْتَمَعَ إلَى</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14700,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>أَكْبرَ</t>
+          <t>أَكْبَر</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14776,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>أَلَّتي</t>
+          <t>أَلَّتِي</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -15043,7 +15047,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>أَلْمَانياَ</t>
+          <t>أَلْمَانِيَا</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15285,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>إَنْتَخَب</t>
+          <t>إِنْتَخَب</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15323,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>إَنْتَظَر</t>
+          <t>إِنْتَظَر</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15946,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>הליגה הערבית)</t>
+          <t>הליגה הערבית</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -17511,7 +17515,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>طَبرَِيَّا</t>
+          <t>طَبَرِيَّا</t>
         </is>
       </c>
     </row>
@@ -17630,7 +17634,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>عَالمَ</t>
+          <t>عَالَم</t>
         </is>
       </c>
     </row>
@@ -18058,7 +18062,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>غَنيِّ</t>
+          <t>غَنِيّ</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -18582,7 +18586,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>لَاَعِب</t>
+          <t>لَاعِب</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -19602,7 +19606,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>مُهَنْدِسَ</t>
+          <t>مُهَنْدِس</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -19873,7 +19877,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>ناية</t>
+          <t>نهاية</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -19883,12 +19887,12 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>נאיה</t>
+          <t>נהאיה</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>نَِاية</t>
+          <t>نِهَاية</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22743,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>تَجََوَّل</t>
+          <t>تَجَوَّل</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22781,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>تَحََدَّث</t>
+          <t>تَحَدَّث</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22956,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>!تفضل</t>
+          <t>تفضل!</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
@@ -22962,12 +22966,12 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>!תפצ׳ל</t>
-        </is>
-      </c>
-      <c r="H559" t="inlineStr">
-        <is>
-          <t>!ْتَفَضَّل</t>
+          <t>תפצ׳ל!</t>
+        </is>
+      </c>
+      <c r="H559" s="10" t="inlineStr">
+        <is>
+          <t>تَفَضَّل!</t>
         </is>
       </c>
     </row>
@@ -23995,7 +23999,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>خَبرَ</t>
+          <t>خَبَر</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -24038,7 +24042,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>خَيرْ</t>
+          <t>خَيْر</t>
         </is>
       </c>
     </row>
@@ -24810,7 +24814,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>سَكَنُ</t>
+          <t>سَكَنَ</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26781,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>قام بزيارةل</t>
+          <t>قام بزيارة ل</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -26787,12 +26791,12 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>קאמ בזיארהל</t>
+          <t>קאמ בזיארה ל</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>قَامَ بِزيَارَةِل</t>
+          <t>قَامَ بِزيَارَة ل</t>
         </is>
       </c>
     </row>
@@ -26815,7 +26819,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>قامبجولة في</t>
+          <t>قام بجولة في</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -26825,12 +26829,12 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>קאמבג׳ולה פי</t>
+          <t>קאמ בג׳ולה פי</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>قَامِبجَِوْلَةَ في</t>
+          <t>قَامَ بِجَوْلَةَ فِي</t>
         </is>
       </c>
     </row>
@@ -27402,7 +27406,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>لأَِن</t>
+          <t>لِأَنَ</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27768,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>مَسْؤُولْ عَن</t>
+          <t>مَسْؤُول عَن</t>
         </is>
       </c>
     </row>
@@ -27878,7 +27882,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>مُسْلِمَ</t>
+          <t>مُسْلِم</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -27921,7 +27925,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>مَسِيحِيَّ</t>
+          <t>مَسِيحِيّ</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -28002,7 +28006,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>مُشْكِلةَ</t>
+          <t>مُشْكِلة</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -28164,7 +28168,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>مَطْلُوبَ</t>
+          <t>مَطْلُوب</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -28579,12 +28583,12 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>مَمَُثِّل</t>
+          <t>مُمَثِّل</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>مَمَُثِّلُونَ / مَمَُثِّلِينَ</t>
+          <t>مُمَثِّلُونَ / مُمَثِّلِينَ</t>
         </is>
       </c>
     </row>
@@ -28736,7 +28740,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>مِنْْ فَضْلِكَ / فَضْلِكُم</t>
+          <t>مِنْ فَضْلِكَ / فَضْلِكُم</t>
         </is>
       </c>
     </row>
@@ -28898,7 +28902,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>مُوَاطِنَ</t>
+          <t>مُوَاطِن</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -29022,7 +29026,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>مُوَظَّفَ</t>
+          <t>مُوَظَّف</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -29151,7 +29155,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>نجََحَ</t>
+          <t>نجَحَ</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29388,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>وَصَلِ</t>
+          <t>وَصَلَ</t>
         </is>
       </c>
     </row>
@@ -29898,7 +29902,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>إِتجََّه / إِتجَِّاه</t>
+          <t>إِتجََّه / إِتجَِّاه</t>
         </is>
       </c>
     </row>
@@ -29936,7 +29940,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>إِتحَِّاد</t>
+          <t>إِتِّحَاد</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29978,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>إِتخََّذَ</t>
+          <t>إِتَخَّذَ</t>
         </is>
       </c>
     </row>
@@ -30478,12 +30482,12 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>إَرْهَابيِّ</t>
+          <t>إَرْهَابِيّ</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>إَرْهَابيُِّونَ / إَرْهَابيِِّينَ</t>
+          <t>إَرْهَابِيُّونَ / إَرْهَابِيِّينَ</t>
         </is>
       </c>
     </row>
@@ -30602,7 +30606,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>إِسْتَمَر / إِسْتَمَرَِّ في</t>
+          <t>إِسْتَمَر / إِسْتَمَرَّ فِي</t>
         </is>
       </c>
     </row>
@@ -30716,7 +30720,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>أَشَارََ إِلى</t>
+          <t>أَشَارَ إِلَى</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30872,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>إِعْتَرَفَِ ب</t>
+          <t>إِعْتَرَفَ بِ</t>
         </is>
       </c>
     </row>
@@ -31681,7 +31685,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>أَهمَِّيَّة</t>
+          <t>أَهمِّيَّة</t>
         </is>
       </c>
     </row>
@@ -31952,7 +31956,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>تّجَِارِي</t>
+          <t>تِّجَارِي</t>
         </is>
       </c>
     </row>
@@ -32408,7 +32412,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>توجهإلى</t>
+          <t>توجه إلى</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
@@ -32418,12 +32422,12 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>תוג׳האלא</t>
+          <t>תוג׳ה אלא</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>تَوَجَّهَإِلىَ</t>
+          <t>تَوَجَّهَ إِلَى</t>
         </is>
       </c>
     </row>
@@ -32942,7 +32946,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>حَتى</t>
+          <t>حَتَى</t>
         </is>
       </c>
     </row>
@@ -33066,7 +33070,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>حَضَرُ</t>
+          <t>حَضَرَ</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
@@ -33775,7 +33779,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>سَمَِعْتُ ذٰلِك</t>
+          <t>سَمِعْتُ ذٰلِك</t>
         </is>
       </c>
     </row>
@@ -33927,7 +33931,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>رَفَضُ</t>
+          <t>رَفَضَ</t>
         </is>
       </c>
     </row>
@@ -34289,12 +34293,12 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>سَمََح</t>
+          <t>سَمَحَ</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
         <is>
-          <t>سَمََحُونَ / سَمََحِينَ</t>
+          <t>سَمَحُونَ / سَمَحِينَ</t>
         </is>
       </c>
     </row>
@@ -34332,7 +34336,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>شَارَك</t>
+          <t>شَارَكَ</t>
         </is>
       </c>
     </row>
@@ -34651,7 +34655,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>ضِد</t>
+          <t>ضِدَ</t>
         </is>
       </c>
     </row>
@@ -35018,7 +35022,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>عَرَضِ عَلَى</t>
+          <t>عَرَضَ عَلَى</t>
         </is>
       </c>
       <c r="L861" t="inlineStr">
@@ -35494,7 +35498,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>قُطَاع غَزَّة</t>
+          <t>قِطَاع غَزَّة</t>
         </is>
       </c>
     </row>
@@ -35694,7 +35698,7 @@
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>لَجْنَة</t>
+          <t>لَجِنَة</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -35813,7 +35817,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>مُؤْتمََرّ صُحُفِي</t>
+          <t>مُؤْتَمَرّ صُحُفِيّ</t>
         </is>
       </c>
     </row>
@@ -35851,7 +35855,7 @@
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>مُؤْتمََر قِمَّة</t>
+          <t>مُؤْتَمَر قِمَّة</t>
         </is>
       </c>
     </row>
@@ -37208,7 +37212,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>نَامََ</t>
+          <t>نَامَ</t>
         </is>
       </c>
     </row>
@@ -37646,12 +37650,12 @@
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>هَدَفََ</t>
+          <t>هَدَفَ</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>هَدَفَُونَ / هَدَفَِينَ</t>
+          <t>هَدَفُونَ / هَدَفِينَ</t>
         </is>
       </c>
     </row>
@@ -37770,7 +37774,7 @@
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>وَجَب يْجَِبَُ أَن</t>
+          <t>وَجَب يَجِبُ أَن</t>
         </is>
       </c>
     </row>
@@ -37975,7 +37979,7 @@
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>وَطَني</t>
+          <t>وَطَنِيّ</t>
         </is>
       </c>
     </row>
@@ -38165,7 +38169,7 @@
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>إِحْتَاجََ إلى</t>
+          <t>إِحْتَاجَ إلَى</t>
         </is>
       </c>
     </row>
@@ -38517,7 +38521,7 @@
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>إِسْتَعَدَِّ ل</t>
+          <t>إِسْتَعَدَّ لِ</t>
         </is>
       </c>
     </row>
@@ -38778,7 +38782,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>إعتبارامن</t>
+          <t>إعتبار من</t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
@@ -38788,12 +38792,12 @@
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>אעתבאראמנ</t>
+          <t>אעתבאר מנ</t>
         </is>
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>إِعْتِبَارًاْمِن</t>
+          <t>إِعْتِبَارً مِن</t>
         </is>
       </c>
     </row>
@@ -39069,7 +39073,7 @@
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>أَلْبَحْرُ الْأَبْيَض الْمُتَوَسِّط</t>
+          <t>أَلْبَحْر الْأَبْيَض الْمُتَوَسِّط</t>
         </is>
       </c>
     </row>
@@ -39811,7 +39815,7 @@
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>بَلَغُ</t>
+          <t>بَلَغَ</t>
         </is>
       </c>
       <c r="L982" t="inlineStr">
@@ -40006,7 +40010,7 @@
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>تَابِعِ ل</t>
+          <t>تَابِع لِ</t>
         </is>
       </c>
     </row>
@@ -40158,7 +40162,7 @@
       </c>
       <c r="H991" t="inlineStr">
         <is>
-          <t>تَمََثَّل</t>
+          <t>تَمَثَّلَ</t>
         </is>
       </c>
     </row>
@@ -40196,7 +40200,7 @@
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>تمََنى</t>
+          <t>تمَنَى</t>
         </is>
       </c>
     </row>
@@ -40796,7 +40800,7 @@
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>حَقَّقَِ مَعَ في</t>
+          <t>حَقَّقَ مَعَ فِي</t>
         </is>
       </c>
     </row>
@@ -40834,7 +40838,7 @@
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>حمََلِ</t>
+          <t>حَمَلَ</t>
         </is>
       </c>
     </row>
@@ -40986,7 +40990,7 @@
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>خُطَّةُ</t>
+          <t>خُطَّة</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -41381,7 +41385,7 @@
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>رَغْبَةًِ في</t>
+          <t>رَغْبَةً فِي</t>
         </is>
       </c>
     </row>
@@ -42305,7 +42309,7 @@
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>صَهْيُوني</t>
+          <t>صَهْيُونيّ</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43061,7 @@
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>قَتَلَُ</t>
+          <t>قَتَلَ</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43337,7 @@
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>كَشَفِ</t>
+          <t>كَشَفَ</t>
         </is>
       </c>
     </row>
@@ -43976,7 +43980,7 @@
       </c>
       <c r="H1087" t="inlineStr">
         <is>
-          <t>مّحََلِّي</t>
+          <t>مَّحَلِّي</t>
         </is>
       </c>
     </row>
@@ -44589,7 +44593,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>منقبل</t>
+          <t>من قبل</t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
@@ -44599,12 +44603,12 @@
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>מנקבל</t>
+          <t>מנ קבל</t>
         </is>
       </c>
       <c r="H1103" t="inlineStr">
         <is>
-          <t>مِنِقِبَلْ</t>
+          <t>مِن قِبَل</t>
         </is>
       </c>
     </row>
@@ -45361,7 +45365,7 @@
       </c>
       <c r="H1122" t="inlineStr">
         <is>
-          <t>هَبَطُ</t>
+          <t>هَبَطَ</t>
         </is>
       </c>
     </row>

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -46519,7 +46519,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَارِسُ</t>
+          <t>تَتَدَارَسُ</t>
         </is>
       </c>
       <c r="B3" s="6" t="n"/>
@@ -46531,7 +46531,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَمِّلِينَ</t>
+          <t>تَتَحَمَّلِينَ</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -46543,7 +46543,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَاهِمُونَ</t>
+          <t>يَتَفَاهَمُونَ</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
@@ -46555,7 +46555,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>تَصَعِّدَا</t>
+          <t>تَصَعَّدَا</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
@@ -46591,7 +46591,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>نَتَضَارِبُ</t>
+          <t>نَتَضَارَبُ</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
@@ -46603,7 +46603,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>تَنَاظِرَا</t>
+          <t>تَنَاظَرَا</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -46723,7 +46723,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>تَعَارِفِي</t>
+          <t>تَعَارَفِي</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
@@ -46759,7 +46759,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>تَنَازِلُوا</t>
+          <t>تَنَازَلُوا</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -46975,7 +46975,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>تَفَهِّمَا</t>
+          <t>تَفَهَّمَا</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -47035,7 +47035,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>تَجَالِسُوا</t>
+          <t>تَجَالَسُوا</t>
         </is>
       </c>
       <c r="B46" s="6" t="n"/>
@@ -47083,7 +47083,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>أَتَحَاكِمُ</t>
+          <t>أَتَحَاكَمُ</t>
         </is>
       </c>
       <c r="B50" s="6" t="n"/>
@@ -47263,7 +47263,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَمِّلَانِ</t>
+          <t>تَتَحَمَّلَانِ</t>
         </is>
       </c>
       <c r="B65" s="6" t="n"/>
@@ -47311,7 +47311,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>أَتَدَاخِلُ</t>
+          <t>أَتَدَاخَلُ</t>
         </is>
       </c>
       <c r="B69" s="6" t="n"/>
@@ -47323,7 +47323,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>تَطَلِّبُوا</t>
+          <t>تَطَلَّبُوا</t>
         </is>
       </c>
       <c r="B70" s="6" t="n"/>
@@ -47347,7 +47347,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَهِّمْنَ</t>
+          <t>يَتَفَهَّمْنَ</t>
         </is>
       </c>
       <c r="B72" s="6" t="n"/>
@@ -47551,7 +47551,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>تَتَخَرِّجَانِ</t>
+          <t>تَتَخَرَّجَانِ</t>
         </is>
       </c>
       <c r="B89" s="6" t="n"/>
@@ -47719,7 +47719,7 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>تَتَصَاعِدُ</t>
+          <t>تَتَصَاعَدُ</t>
         </is>
       </c>
       <c r="B103" s="6" t="n"/>
@@ -47731,7 +47731,7 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>تَخَارِجْ</t>
+          <t>تَخَارَجْ</t>
         </is>
       </c>
       <c r="B104" s="6" t="n"/>
@@ -47755,7 +47755,7 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَافِعَانِ</t>
+          <t>تَتَدَافَعَانِ</t>
         </is>
       </c>
       <c r="B106" s="6" t="n"/>
@@ -47779,7 +47779,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>أَتَطَلِّبُ</t>
+          <t>أَتَطَلَّبُ</t>
         </is>
       </c>
       <c r="B108" s="6" t="n"/>
@@ -47815,7 +47815,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>تَجَمِّعَا</t>
+          <t>تَجَمَّعَا</t>
         </is>
       </c>
       <c r="B111" s="6" t="n"/>
@@ -48139,7 +48139,7 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>تَخَارِجْنَ</t>
+          <t>تَخَارَجْنَ</t>
         </is>
       </c>
       <c r="B138" s="6" t="n"/>
@@ -48175,7 +48175,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>نَتَكَاتِبُ</t>
+          <t>نَتَكَاتَبُ</t>
         </is>
       </c>
       <c r="B141" s="6" t="n"/>
@@ -48331,7 +48331,7 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>يَتَلَبِّسَانِ</t>
+          <t>يَتَلَبَّسَانِ</t>
         </is>
       </c>
       <c r="B154" s="6" t="n"/>
@@ -48427,7 +48427,7 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>تَتَرَاكِبَانِ</t>
+          <t>تَتَرَاكَبَانِ</t>
         </is>
       </c>
       <c r="B162" s="6" t="n"/>
@@ -48559,7 +48559,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>أَتَرَكِّبُ</t>
+          <t>أَتَرَكَّبُ</t>
         </is>
       </c>
       <c r="B173" s="6" t="n"/>
@@ -48607,7 +48607,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>تَتَعَارِفْنَ</t>
+          <t>تَتَعَارَفْنَ</t>
         </is>
       </c>
       <c r="B177" s="6" t="n"/>
@@ -48787,7 +48787,7 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَامِلُ</t>
+          <t>تَتَحَامَلُ</t>
         </is>
       </c>
       <c r="B192" s="6" t="n"/>
@@ -48811,7 +48811,7 @@
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>تَعَامِلْنَ</t>
+          <t>تَعَامَلْنَ</t>
         </is>
       </c>
       <c r="B194" s="6" t="n"/>
@@ -48847,7 +48847,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>يَتَحَامِلْنَ</t>
+          <t>يَتَحَامَلْنَ</t>
         </is>
       </c>
       <c r="B197" s="6" t="n"/>
@@ -48919,7 +48919,7 @@
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>تَجَالِسَا</t>
+          <t>تَجَالَسَا</t>
         </is>
       </c>
       <c r="B203" s="6" t="n"/>
@@ -49015,7 +49015,7 @@
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>تَقَطِّعِي</t>
+          <t>تَقَطَّعِي</t>
         </is>
       </c>
       <c r="B211" s="6" t="n"/>
@@ -49099,7 +49099,7 @@
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَاخِلْنَ</t>
+          <t>تَتَدَاخَلْنَ</t>
         </is>
       </c>
       <c r="B218" s="6" t="n"/>
@@ -49243,7 +49243,7 @@
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>تَتَرَاكِبُ</t>
+          <t>تَتَرَاكَبُ</t>
         </is>
       </c>
       <c r="B230" s="6" t="n"/>
@@ -49291,7 +49291,7 @@
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>نَتَرَاكِبُ</t>
+          <t>نَتَرَاكَبُ</t>
         </is>
       </c>
       <c r="B234" s="6" t="n"/>
@@ -49387,7 +49387,7 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>تَحَمِّلَا</t>
+          <t>تَحَمَّلَا</t>
         </is>
       </c>
       <c r="B242" s="6" t="n"/>
@@ -49423,7 +49423,7 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>يَتَدَارِسُونَ</t>
+          <t>يَتَدَارَسُونَ</t>
         </is>
       </c>
       <c r="B245" s="6" t="n"/>
@@ -49471,7 +49471,7 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>تَتَقَطِّعِينَ</t>
+          <t>تَتَقَطَّعِينَ</t>
         </is>
       </c>
       <c r="B249" s="6" t="n"/>
@@ -49543,7 +49543,7 @@
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>تَطَلِّبَا</t>
+          <t>تَطَلَّبَا</t>
         </is>
       </c>
       <c r="B255" s="6" t="n"/>
@@ -49579,7 +49579,7 @@
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>يَتَكَسِّرْنَ</t>
+          <t>يَتَكَسَّرْنَ</t>
         </is>
       </c>
       <c r="B258" s="6" t="n"/>
@@ -49831,7 +49831,7 @@
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>تَتَقَطِّعُ</t>
+          <t>تَتَقَطَّعُ</t>
         </is>
       </c>
       <c r="B279" s="6" t="n"/>
@@ -49879,7 +49879,7 @@
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>يَتَطَلِّبَانِ</t>
+          <t>يَتَطَلَّبَانِ</t>
         </is>
       </c>
       <c r="B283" s="6" t="n"/>
@@ -49903,7 +49903,7 @@
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>يَتَنَاظِرْنَ</t>
+          <t>يَتَنَاظَرْنَ</t>
         </is>
       </c>
       <c r="B285" s="6" t="n"/>
@@ -49927,7 +49927,7 @@
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>يَتَقَاطِعُ</t>
+          <t>يَتَقَاطَعُ</t>
         </is>
       </c>
       <c r="B287" s="6" t="n"/>
@@ -49987,7 +49987,7 @@
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>يَتَخَرِّجَانِ</t>
+          <t>يَتَخَرَّجَانِ</t>
         </is>
       </c>
       <c r="B292" s="6" t="n"/>
@@ -49999,7 +49999,7 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>يَتَرَاجِعَانِ</t>
+          <t>يَتَرَاجَعَانِ</t>
         </is>
       </c>
       <c r="B293" s="6" t="n"/>
@@ -50047,7 +50047,7 @@
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>نَتَخَرِّجُ</t>
+          <t>نَتَخَرَّجُ</t>
         </is>
       </c>
       <c r="B297" s="6" t="n"/>
@@ -50107,7 +50107,7 @@
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَاكِمَانِ</t>
+          <t>تَتَحَاكَمَانِ</t>
         </is>
       </c>
       <c r="B302" s="6" t="n"/>
@@ -50167,7 +50167,7 @@
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>تَدَافِعَا</t>
+          <t>تَدَافَعَا</t>
         </is>
       </c>
       <c r="B307" s="6" t="n"/>
@@ -50383,7 +50383,7 @@
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>تَدَاخِلَا</t>
+          <t>تَدَاخَلَا</t>
         </is>
       </c>
       <c r="B325" s="6" t="n"/>
@@ -50407,7 +50407,7 @@
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
         <is>
-          <t>تَتَعَامِلَانِ</t>
+          <t>تَتَعَامَلَانِ</t>
         </is>
       </c>
       <c r="B327" s="6" t="n"/>
@@ -50863,7 +50863,7 @@
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
         <is>
-          <t>أَتَجَالِسُ</t>
+          <t>أَتَجَالَسُ</t>
         </is>
       </c>
       <c r="B365" s="6" t="n"/>
@@ -50887,7 +50887,7 @@
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَخِّلْنَ</t>
+          <t>تَتَدَخَّلْنَ</t>
         </is>
       </c>
       <c r="B367" s="6" t="n"/>
@@ -50911,7 +50911,7 @@
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَاهِمُ</t>
+          <t>يَتَفَاهَمُ</t>
         </is>
       </c>
       <c r="B369" s="6" t="n"/>
@@ -50995,7 +50995,7 @@
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
         <is>
-          <t>يَتَصَاعِدَانِ</t>
+          <t>يَتَصَاعَدَانِ</t>
         </is>
       </c>
       <c r="B376" s="6" t="n"/>
@@ -51019,7 +51019,7 @@
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
         <is>
-          <t>تَتَكَاتِبُ</t>
+          <t>تَتَكَاتَبُ</t>
         </is>
       </c>
       <c r="B378" s="6" t="n"/>
@@ -51043,7 +51043,7 @@
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
         <is>
-          <t>تَتَشَرِّبَانِ</t>
+          <t>تَتَشَرَّبَانِ</t>
         </is>
       </c>
       <c r="B380" s="6" t="n"/>
@@ -51079,7 +51079,7 @@
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
         <is>
-          <t>تَتَجَمِّعُونَ</t>
+          <t>تَتَجَمَّعُونَ</t>
         </is>
       </c>
       <c r="B383" s="6" t="n"/>
@@ -51091,7 +51091,7 @@
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
         <is>
-          <t>تَحَفِّظْ</t>
+          <t>تَحَفَّظْ</t>
         </is>
       </c>
       <c r="B384" s="6" t="n"/>
@@ -51235,7 +51235,7 @@
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
         <is>
-          <t>يَتَخَارِجَانِ</t>
+          <t>يَتَخَارَجَانِ</t>
         </is>
       </c>
       <c r="B396" s="6" t="n"/>
@@ -51247,7 +51247,7 @@
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
         <is>
-          <t>يَتَعَرِّفُونَ</t>
+          <t>يَتَعَرَّفُونَ</t>
         </is>
       </c>
       <c r="B397" s="6" t="n"/>
@@ -51331,7 +51331,7 @@
     <row r="404">
       <c r="A404" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَافِعُ</t>
+          <t>تَتَدَافَعُ</t>
         </is>
       </c>
       <c r="B404" s="6" t="n"/>
@@ -51439,7 +51439,7 @@
     <row r="413">
       <c r="A413" s="5" t="inlineStr">
         <is>
-          <t>تَنَازِلْ</t>
+          <t>تَنَازَلْ</t>
         </is>
       </c>
       <c r="B413" s="6" t="n"/>
@@ -51451,7 +51451,7 @@
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
         <is>
-          <t>تَقَاطِعِي</t>
+          <t>تَقَاطَعِي</t>
         </is>
       </c>
       <c r="B414" s="6" t="n"/>
@@ -51751,7 +51751,7 @@
     <row r="439">
       <c r="A439" s="5" t="inlineStr">
         <is>
-          <t>أَتَسَامِعُ</t>
+          <t>أَتَسَامَعُ</t>
         </is>
       </c>
       <c r="B439" s="6" t="n"/>
@@ -51763,7 +51763,7 @@
     <row r="440">
       <c r="A440" s="5" t="inlineStr">
         <is>
-          <t>تَحَامِلُوا</t>
+          <t>تَحَامَلُوا</t>
         </is>
       </c>
       <c r="B440" s="6" t="n"/>
@@ -51787,7 +51787,7 @@
     <row r="442">
       <c r="A442" s="5" t="inlineStr">
         <is>
-          <t>يَتَدَارِسُ</t>
+          <t>يَتَدَارَسُ</t>
         </is>
       </c>
       <c r="B442" s="6" t="n"/>
@@ -51799,7 +51799,7 @@
     <row r="443">
       <c r="A443" s="5" t="inlineStr">
         <is>
-          <t>تَتَنَاظِرِينَ</t>
+          <t>تَتَنَاظَرِينَ</t>
         </is>
       </c>
       <c r="B443" s="6" t="n"/>
@@ -51859,7 +51859,7 @@
     <row r="448">
       <c r="A448" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَاهِمَانِ</t>
+          <t>يَتَفَاهَمَانِ</t>
         </is>
       </c>
       <c r="B448" s="6" t="n"/>
@@ -51943,7 +51943,7 @@
     <row r="455">
       <c r="A455" s="5" t="inlineStr">
         <is>
-          <t>يَتَلَاعِبُونَ</t>
+          <t>يَتَلَاعَبُونَ</t>
         </is>
       </c>
       <c r="B455" s="6" t="n"/>
@@ -52003,7 +52003,7 @@
     <row r="460">
       <c r="A460" s="5" t="inlineStr">
         <is>
-          <t>تَتَفَهِّمِينَ</t>
+          <t>تَتَفَهَّمِينَ</t>
         </is>
       </c>
       <c r="B460" s="6" t="n"/>
@@ -52243,7 +52243,7 @@
     <row r="480">
       <c r="A480" s="5" t="inlineStr">
         <is>
-          <t>تَتَجَمِّعِينَ</t>
+          <t>تَتَجَمَّعِينَ</t>
         </is>
       </c>
       <c r="B480" s="6" t="n"/>
@@ -52387,7 +52387,7 @@
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
         <is>
-          <t>تَكَاتِبْ</t>
+          <t>تَكَاتَبْ</t>
         </is>
       </c>
       <c r="B492" s="6" t="n"/>
@@ -52399,7 +52399,7 @@
     <row r="493">
       <c r="A493" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَامِلُونَ</t>
+          <t>تَتَحَامَلُونَ</t>
         </is>
       </c>
       <c r="B493" s="6" t="n"/>
@@ -52447,7 +52447,7 @@
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَامِلْنَ</t>
+          <t>تَتَحَامَلْنَ</t>
         </is>
       </c>
       <c r="B497" s="6" t="n"/>
@@ -53193,7 +53193,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَارِسُ</t>
+          <t>تَتَدَارَسُ</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -53225,7 +53225,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَمِّلِينَ</t>
+          <t>تَتَحَمَّلِينَ</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -53257,7 +53257,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَاهِمُونَ</t>
+          <t>يَتَفَاهَمُونَ</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -53289,7 +53289,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>تَصَعِّدَا</t>
+          <t>تَصَعَّدَا</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -53385,7 +53385,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>نَتَضَارِبُ</t>
+          <t>نَتَضَارَبُ</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -53417,7 +53417,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>تَنَاظِرَا</t>
+          <t>تَنَاظَرَا</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -53737,7 +53737,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>تَعَارِفِي</t>
+          <t>تَعَارَفِي</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -53833,7 +53833,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>تَنَازِلُوا</t>
+          <t>تَنَازَلُوا</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -54409,7 +54409,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>تَفَهِّمَا</t>
+          <t>تَفَهَّمَا</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -54569,7 +54569,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>تَجَالِسُوا</t>
+          <t>تَجَالَسُوا</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -54697,7 +54697,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>أَتَحَاكِمُ</t>
+          <t>أَتَحَاكَمُ</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -55177,7 +55177,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَمِّلَانِ</t>
+          <t>تَتَحَمَّلَانِ</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -55305,7 +55305,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>أَتَدَاخِلُ</t>
+          <t>أَتَدَاخَلُ</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -55337,7 +55337,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>تَطَلِّبُوا</t>
+          <t>تَطَلَّبُوا</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -55401,7 +55401,7 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَهِّمْنَ</t>
+          <t>يَتَفَهَّمْنَ</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -55945,7 +55945,7 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>تَتَخَرِّجَانِ</t>
+          <t>تَتَخَرَّجَانِ</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -56393,7 +56393,7 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>تَتَصَاعِدُ</t>
+          <t>تَتَصَاعَدُ</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -56425,7 +56425,7 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>تَخَارِجْ</t>
+          <t>تَخَارَجْ</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -56489,7 +56489,7 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَافِعَانِ</t>
+          <t>تَتَدَافَعَانِ</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -56553,7 +56553,7 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>أَتَطَلِّبُ</t>
+          <t>أَتَطَلَّبُ</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -56649,7 +56649,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>تَجَمِّعَا</t>
+          <t>تَجَمَّعَا</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -57513,7 +57513,7 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>تَخَارِجْنَ</t>
+          <t>تَخَارَجْنَ</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
@@ -57609,7 +57609,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>نَتَكَاتِبُ</t>
+          <t>نَتَكَاتَبُ</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -58025,7 +58025,7 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>يَتَلَبِّسَانِ</t>
+          <t>يَتَلَبَّسَانِ</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -58281,7 +58281,7 @@
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>تَتَرَاكِبَانِ</t>
+          <t>تَتَرَاكَبَانِ</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -58633,7 +58633,7 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>أَتَرَكِّبُ</t>
+          <t>أَتَرَكَّبُ</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
@@ -58761,7 +58761,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>تَتَعَارِفْنَ</t>
+          <t>تَتَعَارَفْنَ</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -59241,7 +59241,7 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَامِلُ</t>
+          <t>تَتَحَامَلُ</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -59305,7 +59305,7 @@
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>تَعَامِلْنَ</t>
+          <t>تَعَامَلْنَ</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
@@ -59401,7 +59401,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>يَتَحَامِلْنَ</t>
+          <t>يَتَحَامَلْنَ</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -59593,7 +59593,7 @@
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>تَجَالِسَا</t>
+          <t>تَجَالَسَا</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
@@ -59849,7 +59849,7 @@
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>تَقَطِّعِي</t>
+          <t>تَقَطَّعِي</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
@@ -60073,7 +60073,7 @@
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَاخِلْنَ</t>
+          <t>تَتَدَاخَلْنَ</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
@@ -60457,7 +60457,7 @@
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>تَتَرَاكِبُ</t>
+          <t>تَتَرَاكَبُ</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
@@ -60585,7 +60585,7 @@
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>نَتَرَاكِبُ</t>
+          <t>نَتَرَاكَبُ</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
@@ -60841,7 +60841,7 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>تَحَمِّلَا</t>
+          <t>تَحَمَّلَا</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
@@ -60937,7 +60937,7 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>يَتَدَارِسُونَ</t>
+          <t>يَتَدَارَسُونَ</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
@@ -61065,7 +61065,7 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>تَتَقَطِّعِينَ</t>
+          <t>تَتَقَطَّعِينَ</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
@@ -61257,7 +61257,7 @@
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>تَطَلِّبَا</t>
+          <t>تَطَلَّبَا</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
@@ -61353,7 +61353,7 @@
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>يَتَكَسِّرْنَ</t>
+          <t>يَتَكَسَّرْنَ</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
@@ -62025,7 +62025,7 @@
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>تَتَقَطِّعُ</t>
+          <t>تَتَقَطَّعُ</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -62153,7 +62153,7 @@
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>يَتَطَلِّبَانِ</t>
+          <t>يَتَطَلَّبَانِ</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -62217,7 +62217,7 @@
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>يَتَنَاظِرْنَ</t>
+          <t>يَتَنَاظَرْنَ</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -62281,7 +62281,7 @@
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>يَتَقَاطِعُ</t>
+          <t>يَتَقَاطَعُ</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -62441,7 +62441,7 @@
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>يَتَخَرِّجَانِ</t>
+          <t>يَتَخَرَّجَانِ</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -62473,7 +62473,7 @@
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>يَتَرَاجِعَانِ</t>
+          <t>يَتَرَاجَعَانِ</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -62601,7 +62601,7 @@
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>نَتَخَرِّجُ</t>
+          <t>نَتَخَرَّجُ</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -62761,7 +62761,7 @@
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَاكِمَانِ</t>
+          <t>تَتَحَاكَمَانِ</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
@@ -62921,7 +62921,7 @@
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>تَدَافِعَا</t>
+          <t>تَدَافَعَا</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
@@ -63497,7 +63497,7 @@
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>تَدَاخِلَا</t>
+          <t>تَدَاخَلَا</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
@@ -63561,7 +63561,7 @@
     <row r="327">
       <c r="A327" s="5" t="inlineStr">
         <is>
-          <t>تَتَعَامِلَانِ</t>
+          <t>تَتَعَامَلَانِ</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
@@ -64777,7 +64777,7 @@
     <row r="365">
       <c r="A365" s="5" t="inlineStr">
         <is>
-          <t>أَتَجَالِسُ</t>
+          <t>أَتَجَالَسُ</t>
         </is>
       </c>
       <c r="B365" s="5" t="inlineStr">
@@ -64841,7 +64841,7 @@
     <row r="367">
       <c r="A367" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَخِّلْنَ</t>
+          <t>تَتَدَخَّلْنَ</t>
         </is>
       </c>
       <c r="B367" s="5" t="inlineStr">
@@ -64905,7 +64905,7 @@
     <row r="369">
       <c r="A369" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَاهِمُ</t>
+          <t>يَتَفَاهَمُ</t>
         </is>
       </c>
       <c r="B369" s="5" t="inlineStr">
@@ -65129,7 +65129,7 @@
     <row r="376">
       <c r="A376" s="5" t="inlineStr">
         <is>
-          <t>يَتَصَاعِدَانِ</t>
+          <t>يَتَصَاعَدَانِ</t>
         </is>
       </c>
       <c r="B376" s="5" t="inlineStr">
@@ -65193,7 +65193,7 @@
     <row r="378">
       <c r="A378" s="5" t="inlineStr">
         <is>
-          <t>تَتَكَاتِبُ</t>
+          <t>تَتَكَاتَبُ</t>
         </is>
       </c>
       <c r="B378" s="5" t="inlineStr">
@@ -65257,7 +65257,7 @@
     <row r="380">
       <c r="A380" s="5" t="inlineStr">
         <is>
-          <t>تَتَشَرِّبَانِ</t>
+          <t>تَتَشَرَّبَانِ</t>
         </is>
       </c>
       <c r="B380" s="5" t="inlineStr">
@@ -65353,7 +65353,7 @@
     <row r="383">
       <c r="A383" s="5" t="inlineStr">
         <is>
-          <t>تَتَجَمِّعُونَ</t>
+          <t>تَتَجَمَّعُونَ</t>
         </is>
       </c>
       <c r="B383" s="5" t="inlineStr">
@@ -65385,7 +65385,7 @@
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
         <is>
-          <t>تَحَفِّظْ</t>
+          <t>تَحَفَّظْ</t>
         </is>
       </c>
       <c r="B384" s="5" t="inlineStr">
@@ -65769,7 +65769,7 @@
     <row r="396">
       <c r="A396" s="5" t="inlineStr">
         <is>
-          <t>يَتَخَارِجَانِ</t>
+          <t>يَتَخَارَجَانِ</t>
         </is>
       </c>
       <c r="B396" s="5" t="inlineStr">
@@ -65801,7 +65801,7 @@
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
         <is>
-          <t>يَتَعَرِّفُونَ</t>
+          <t>يَتَعَرَّفُونَ</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
@@ -66025,7 +66025,7 @@
     <row r="404">
       <c r="A404" s="5" t="inlineStr">
         <is>
-          <t>تَتَدَافِعُ</t>
+          <t>تَتَدَافَعُ</t>
         </is>
       </c>
       <c r="B404" s="5" t="inlineStr">
@@ -66313,7 +66313,7 @@
     <row r="413">
       <c r="A413" s="5" t="inlineStr">
         <is>
-          <t>تَنَازِلْ</t>
+          <t>تَنَازَلْ</t>
         </is>
       </c>
       <c r="B413" s="5" t="inlineStr">
@@ -66345,7 +66345,7 @@
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
         <is>
-          <t>تَقَاطِعِي</t>
+          <t>تَقَاطَعِي</t>
         </is>
       </c>
       <c r="B414" s="5" t="inlineStr">
@@ -67145,7 +67145,7 @@
     <row r="439">
       <c r="A439" s="5" t="inlineStr">
         <is>
-          <t>أَتَسَامِعُ</t>
+          <t>أَتَسَامَعُ</t>
         </is>
       </c>
       <c r="B439" s="5" t="inlineStr">
@@ -67177,7 +67177,7 @@
     <row r="440">
       <c r="A440" s="5" t="inlineStr">
         <is>
-          <t>تَحَامِلُوا</t>
+          <t>تَحَامَلُوا</t>
         </is>
       </c>
       <c r="B440" s="5" t="inlineStr">
@@ -67241,7 +67241,7 @@
     <row r="442">
       <c r="A442" s="5" t="inlineStr">
         <is>
-          <t>يَتَدَارِسُ</t>
+          <t>يَتَدَارَسُ</t>
         </is>
       </c>
       <c r="B442" s="5" t="inlineStr">
@@ -67273,7 +67273,7 @@
     <row r="443">
       <c r="A443" s="5" t="inlineStr">
         <is>
-          <t>تَتَنَاظِرِينَ</t>
+          <t>تَتَنَاظَرِينَ</t>
         </is>
       </c>
       <c r="B443" s="5" t="inlineStr">
@@ -67433,7 +67433,7 @@
     <row r="448">
       <c r="A448" s="5" t="inlineStr">
         <is>
-          <t>يَتَفَاهِمَانِ</t>
+          <t>يَتَفَاهَمَانِ</t>
         </is>
       </c>
       <c r="B448" s="5" t="inlineStr">
@@ -67657,7 +67657,7 @@
     <row r="455">
       <c r="A455" s="5" t="inlineStr">
         <is>
-          <t>يَتَلَاعِبُونَ</t>
+          <t>يَتَلَاعَبُونَ</t>
         </is>
       </c>
       <c r="B455" s="5" t="inlineStr">
@@ -67817,7 +67817,7 @@
     <row r="460">
       <c r="A460" s="5" t="inlineStr">
         <is>
-          <t>تَتَفَهِّمِينَ</t>
+          <t>تَتَفَهَّمِينَ</t>
         </is>
       </c>
       <c r="B460" s="5" t="inlineStr">
@@ -68457,7 +68457,7 @@
     <row r="480">
       <c r="A480" s="5" t="inlineStr">
         <is>
-          <t>تَتَجَمِّعِينَ</t>
+          <t>تَتَجَمَّعِينَ</t>
         </is>
       </c>
       <c r="B480" s="5" t="inlineStr">
@@ -68841,7 +68841,7 @@
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
         <is>
-          <t>تَكَاتِبْ</t>
+          <t>تَكَاتَبْ</t>
         </is>
       </c>
       <c r="B492" s="5" t="inlineStr">
@@ -68873,7 +68873,7 @@
     <row r="493">
       <c r="A493" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَامِلُونَ</t>
+          <t>تَتَحَامَلُونَ</t>
         </is>
       </c>
       <c r="B493" s="5" t="inlineStr">
@@ -69001,7 +69001,7 @@
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
         <is>
-          <t>تَتَحَامِلْنَ</t>
+          <t>تَتَحَامَلْنَ</t>
         </is>
       </c>
       <c r="B497" s="5" t="inlineStr">

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -42518,7 +42518,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ד'הב</t>
+          <t>ד׳הב</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -42550,7 +42550,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>רג'ע</t>
+          <t>רג׳ע</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ח'רג'</t>
+          <t>ח׳רג׳</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -42614,7 +42614,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>דח'ל</t>
+          <t>דח׳ל</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -42646,7 +42646,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ג'לס</t>
+          <t>ג׳לס</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -42678,7 +42678,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>נז'ר</t>
+          <t>נז׳ר</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -42838,7 +42838,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ע'לק</t>
+          <t>ע׳לק</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -42934,7 +42934,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>חפז'</t>
+          <t>חפז׳</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -42998,7 +42998,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ע'סל</t>
+          <t>ע׳סל</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -43158,7 +43158,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ח'דמ</t>
+          <t>ח׳דמ</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -43222,7 +43222,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>טבח'</t>
+          <t>טבח׳</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ג'מע</t>
+          <t>ג׳מע</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -43414,7 +43414,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>דרב</t>
+          <t>צ׳רב</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -43478,7 +43478,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>נג'ח</t>
+          <t>נג׳ח</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -43574,7 +43574,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>דחכ</t>
+          <t>צ׳חכ</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -43660,7 +43660,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>הערה: התעתיק הוא תעתיק אותיות (עיצורי) המבוסס על הכתיב הערבי - תנועות קצרות אינן מסומנות (כמו בכתיב ערבי לא מנוקד), ותנועות ארוכות מסומנות באמות קריאה (א/ו/י). האותיות ص/ض מתועתקות שתיהן כ-'צ'/'ד' בקירוב; לצליל המדויק יש להתבסס על הכתיב הערבי.</t>
+          <t>הערה: התעתיק הוא תעתיק אותיות (עיצורי) המבוסס על הכתיב הערבי - תנועות קצרות אינן מסומנות (כמו בכתיב ערבי לא מנוקד), ותנועות ארוכות מסומנות באמות קריאה (א/ו/י). ص מתועתקת כ-'צ' ו-ض כ-'צ׳' (עם גרש) כדי להבחין ביניהן.</t>
         </is>
       </c>
     </row>

--- a/אוצר_מילים_ערבית.xlsx
+++ b/אוצר_מילים_ערבית.xlsx
@@ -42678,7 +42678,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>נז׳ר</t>
+          <t>נט׳ר</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -42934,7 +42934,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>חפז׳</t>
+          <t>חפט׳</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
